--- a/design/蛋仔--大富翁--地块表.xlsx
+++ b/design/蛋仔--大富翁--地块表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\策划文档\大富翁\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\eggitor\1_开发中\大富翁\monopoly\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{514DD49F-FE93-4D62-BE17-A6573E970695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DE3205-69BD-4353-8A3E-7DFD99CEA8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="140">
   <si>
     <t>整数</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -580,6 +580,18 @@
   </si>
   <si>
     <t>4,8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2744,9 +2756,11 @@
         <v>52</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E38" s="3"/>
+        <v>61</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="F38" s="4">
         <v>0</v>
       </c>
@@ -2792,7 +2806,9 @@
       <c r="D39" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="3"/>
+      <c r="E39" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="F39" s="4">
         <v>0</v>
       </c>
@@ -2836,9 +2852,11 @@
         <v>54</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E40" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>138</v>
+      </c>
       <c r="F40" s="4">
         <v>0</v>
       </c>

--- a/design/蛋仔--大富翁--地块表.xlsx
+++ b/design/蛋仔--大富翁--地块表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\eggitor\1_开发中\大富翁\monopoly\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DE3205-69BD-4353-8A3E-7DFD99CEA8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F77281-ED16-49F1-8C05-F7B6937E336D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1087,32 +1087,32 @@
         <v>1000</v>
       </c>
       <c r="G3" s="4">
-        <f>F3*2</f>
-        <v>2000</v>
+        <f>F3</f>
+        <v>1000</v>
       </c>
       <c r="H3" s="4">
         <f t="shared" ref="H3:I3" si="0">G3*2</f>
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="I3" s="4">
         <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="J3" s="4">
+        <f>F3*0.5</f>
+        <v>500</v>
+      </c>
+      <c r="K3" s="4">
+        <f>(F3+G3)*0.5</f>
+        <v>1000</v>
+      </c>
+      <c r="L3" s="4">
+        <f>(F3+G3+H3)*0.75</f>
+        <v>3000</v>
+      </c>
+      <c r="M3" s="4">
+        <f>F3+G3+H3+I3</f>
         <v>8000</v>
-      </c>
-      <c r="J3" s="4">
-        <f>F3/2</f>
-        <v>500</v>
-      </c>
-      <c r="K3" s="4">
-        <f t="shared" ref="K3:M3" si="1">G3/2</f>
-        <v>1000</v>
-      </c>
-      <c r="L3" s="4">
-        <f t="shared" si="1"/>
-        <v>2000</v>
-      </c>
-      <c r="M3" s="4">
-        <f t="shared" si="1"/>
-        <v>4000</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
@@ -1135,32 +1135,32 @@
         <v>1050</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" ref="G4:I4" si="2">F4*2</f>
+        <f t="shared" ref="G4:G36" si="1">F4</f>
+        <v>1050</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" ref="G4:I4" si="2">G4*2</f>
         <v>2100</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <f t="shared" si="2"/>
         <v>4200</v>
       </c>
-      <c r="I4" s="4">
-        <f t="shared" si="2"/>
+      <c r="J4" s="4">
+        <f t="shared" ref="J4:J36" si="3">F4*0.5</f>
+        <v>525</v>
+      </c>
+      <c r="K4" s="4">
+        <f t="shared" ref="K4:K36" si="4">(F4+G4)*0.5</f>
+        <v>1050</v>
+      </c>
+      <c r="L4" s="4">
+        <f t="shared" ref="L4:L36" si="5">(F4+G4+H4)*0.75</f>
+        <v>3150</v>
+      </c>
+      <c r="M4" s="4">
+        <f t="shared" ref="M4:M36" si="6">F4+G4+H4+I4</f>
         <v>8400</v>
-      </c>
-      <c r="J4" s="4">
-        <f t="shared" ref="J4:J36" si="3">F4/2</f>
-        <v>525</v>
-      </c>
-      <c r="K4" s="4">
-        <f t="shared" ref="K4:K36" si="4">G4/2</f>
-        <v>1050</v>
-      </c>
-      <c r="L4" s="4">
-        <f t="shared" ref="L4:L36" si="5">H4/2</f>
-        <v>2100</v>
-      </c>
-      <c r="M4" s="4">
-        <f t="shared" ref="M4:M36" si="6">I4/2</f>
-        <v>4200</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
@@ -1183,16 +1183,16 @@
         <v>1100</v>
       </c>
       <c r="G5" s="4">
-        <f t="shared" ref="G5:I5" si="7">F5*2</f>
+        <f t="shared" si="1"/>
+        <v>1100</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" ref="G5:I5" si="7">G5*2</f>
         <v>2200</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="4">
         <f t="shared" si="7"/>
         <v>4400</v>
-      </c>
-      <c r="I5" s="4">
-        <f t="shared" si="7"/>
-        <v>8800</v>
       </c>
       <c r="J5" s="4">
         <f t="shared" si="3"/>
@@ -1204,11 +1204,11 @@
       </c>
       <c r="L5" s="4">
         <f t="shared" si="5"/>
-        <v>2200</v>
+        <v>3300</v>
       </c>
       <c r="M5" s="4">
         <f t="shared" si="6"/>
-        <v>4400</v>
+        <v>8800</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
@@ -1231,16 +1231,16 @@
         <v>1150</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" ref="G6:I6" si="8">F6*2</f>
+        <f t="shared" si="1"/>
+        <v>1150</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" ref="G6:I6" si="8">G6*2</f>
         <v>2300</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
         <f t="shared" si="8"/>
         <v>4600</v>
-      </c>
-      <c r="I6" s="4">
-        <f t="shared" si="8"/>
-        <v>9200</v>
       </c>
       <c r="J6" s="4">
         <f t="shared" si="3"/>
@@ -1252,11 +1252,11 @@
       </c>
       <c r="L6" s="4">
         <f t="shared" si="5"/>
-        <v>2300</v>
+        <v>3450</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" si="6"/>
-        <v>4600</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
@@ -1279,16 +1279,16 @@
         <v>1200</v>
       </c>
       <c r="G7" s="4">
-        <f t="shared" ref="G7:I7" si="9">F7*2</f>
+        <f t="shared" si="1"/>
+        <v>1200</v>
+      </c>
+      <c r="H7" s="4">
+        <f t="shared" ref="G7:I7" si="9">G7*2</f>
         <v>2400</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
         <f t="shared" si="9"/>
         <v>4800</v>
-      </c>
-      <c r="I7" s="4">
-        <f t="shared" si="9"/>
-        <v>9600</v>
       </c>
       <c r="J7" s="4">
         <f t="shared" si="3"/>
@@ -1300,11 +1300,11 @@
       </c>
       <c r="L7" s="4">
         <f t="shared" si="5"/>
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="M7" s="4">
         <f t="shared" si="6"/>
-        <v>4800</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
@@ -1327,16 +1327,16 @@
         <v>1250</v>
       </c>
       <c r="G8" s="4">
-        <f t="shared" ref="G8:I8" si="10">F8*2</f>
+        <f t="shared" si="1"/>
+        <v>1250</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" ref="G8:I8" si="10">G8*2</f>
         <v>2500</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="4">
         <f t="shared" si="10"/>
         <v>5000</v>
-      </c>
-      <c r="I8" s="4">
-        <f t="shared" si="10"/>
-        <v>10000</v>
       </c>
       <c r="J8" s="4">
         <f t="shared" si="3"/>
@@ -1348,11 +1348,11 @@
       </c>
       <c r="L8" s="4">
         <f t="shared" si="5"/>
-        <v>2500</v>
+        <v>3750</v>
       </c>
       <c r="M8" s="4">
         <f t="shared" si="6"/>
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
@@ -1375,16 +1375,16 @@
         <v>1300</v>
       </c>
       <c r="G9" s="4">
-        <f t="shared" ref="G9:I9" si="11">F9*2</f>
+        <f t="shared" si="1"/>
+        <v>1300</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" ref="G9:I9" si="11">G9*2</f>
         <v>2600</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4">
         <f t="shared" si="11"/>
         <v>5200</v>
-      </c>
-      <c r="I9" s="4">
-        <f t="shared" si="11"/>
-        <v>10400</v>
       </c>
       <c r="J9" s="4">
         <f t="shared" si="3"/>
@@ -1396,11 +1396,11 @@
       </c>
       <c r="L9" s="4">
         <f t="shared" si="5"/>
-        <v>2600</v>
+        <v>3900</v>
       </c>
       <c r="M9" s="4">
         <f t="shared" si="6"/>
-        <v>5200</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
@@ -1423,16 +1423,16 @@
         <v>1350</v>
       </c>
       <c r="G10" s="4">
-        <f t="shared" ref="G10:I10" si="12">F10*2</f>
+        <f t="shared" si="1"/>
+        <v>1350</v>
+      </c>
+      <c r="H10" s="4">
+        <f t="shared" ref="G10:I10" si="12">G10*2</f>
         <v>2700</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4">
         <f t="shared" si="12"/>
         <v>5400</v>
-      </c>
-      <c r="I10" s="4">
-        <f t="shared" si="12"/>
-        <v>10800</v>
       </c>
       <c r="J10" s="4">
         <f t="shared" si="3"/>
@@ -1444,11 +1444,11 @@
       </c>
       <c r="L10" s="4">
         <f t="shared" si="5"/>
-        <v>2700</v>
+        <v>4050</v>
       </c>
       <c r="M10" s="4">
         <f t="shared" si="6"/>
-        <v>5400</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
@@ -1471,16 +1471,16 @@
         <v>1500</v>
       </c>
       <c r="G11" s="4">
-        <f t="shared" ref="G11:I11" si="13">F11*2</f>
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="H11" s="4">
+        <f t="shared" ref="G11:I11" si="13">G11*2</f>
         <v>3000</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <f t="shared" si="13"/>
         <v>6000</v>
-      </c>
-      <c r="I11" s="4">
-        <f t="shared" si="13"/>
-        <v>12000</v>
       </c>
       <c r="J11" s="4">
         <f t="shared" si="3"/>
@@ -1492,11 +1492,11 @@
       </c>
       <c r="L11" s="4">
         <f t="shared" si="5"/>
-        <v>3000</v>
+        <v>4500</v>
       </c>
       <c r="M11" s="4">
         <f t="shared" si="6"/>
-        <v>6000</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
@@ -1519,16 +1519,16 @@
         <v>1600</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" ref="G12:I12" si="14">F12*2</f>
+        <f t="shared" si="1"/>
+        <v>1600</v>
+      </c>
+      <c r="H12" s="4">
+        <f t="shared" ref="G12:I12" si="14">G12*2</f>
         <v>3200</v>
       </c>
-      <c r="H12" s="4">
+      <c r="I12" s="4">
         <f t="shared" si="14"/>
         <v>6400</v>
-      </c>
-      <c r="I12" s="4">
-        <f t="shared" si="14"/>
-        <v>12800</v>
       </c>
       <c r="J12" s="4">
         <f t="shared" si="3"/>
@@ -1540,11 +1540,11 @@
       </c>
       <c r="L12" s="4">
         <f t="shared" si="5"/>
-        <v>3200</v>
+        <v>4800</v>
       </c>
       <c r="M12" s="4">
         <f t="shared" si="6"/>
-        <v>6400</v>
+        <v>12800</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
@@ -1567,16 +1567,16 @@
         <v>1700</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" ref="G13:I13" si="15">F13*2</f>
+        <f t="shared" si="1"/>
+        <v>1700</v>
+      </c>
+      <c r="H13" s="4">
+        <f t="shared" ref="G13:I13" si="15">G13*2</f>
         <v>3400</v>
       </c>
-      <c r="H13" s="4">
+      <c r="I13" s="4">
         <f t="shared" si="15"/>
         <v>6800</v>
-      </c>
-      <c r="I13" s="4">
-        <f t="shared" si="15"/>
-        <v>13600</v>
       </c>
       <c r="J13" s="4">
         <f t="shared" si="3"/>
@@ -1588,11 +1588,11 @@
       </c>
       <c r="L13" s="4">
         <f t="shared" si="5"/>
-        <v>3400</v>
+        <v>5100</v>
       </c>
       <c r="M13" s="4">
         <f t="shared" si="6"/>
-        <v>6800</v>
+        <v>13600</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
@@ -1615,16 +1615,16 @@
         <v>1800</v>
       </c>
       <c r="G14" s="4">
-        <f t="shared" ref="G14:I14" si="16">F14*2</f>
+        <f t="shared" si="1"/>
+        <v>1800</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" ref="G14:I14" si="16">G14*2</f>
         <v>3600</v>
       </c>
-      <c r="H14" s="4">
+      <c r="I14" s="4">
         <f t="shared" si="16"/>
         <v>7200</v>
-      </c>
-      <c r="I14" s="4">
-        <f t="shared" si="16"/>
-        <v>14400</v>
       </c>
       <c r="J14" s="4">
         <f t="shared" si="3"/>
@@ -1636,11 +1636,11 @@
       </c>
       <c r="L14" s="4">
         <f t="shared" si="5"/>
-        <v>3600</v>
+        <v>5400</v>
       </c>
       <c r="M14" s="4">
         <f t="shared" si="6"/>
-        <v>7200</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
@@ -1663,16 +1663,16 @@
         <v>1900</v>
       </c>
       <c r="G15" s="4">
-        <f t="shared" ref="G15:I15" si="17">F15*2</f>
+        <f t="shared" si="1"/>
+        <v>1900</v>
+      </c>
+      <c r="H15" s="4">
+        <f t="shared" ref="G15:I15" si="17">G15*2</f>
         <v>3800</v>
       </c>
-      <c r="H15" s="4">
+      <c r="I15" s="4">
         <f t="shared" si="17"/>
         <v>7600</v>
-      </c>
-      <c r="I15" s="4">
-        <f t="shared" si="17"/>
-        <v>15200</v>
       </c>
       <c r="J15" s="4">
         <f t="shared" si="3"/>
@@ -1684,11 +1684,11 @@
       </c>
       <c r="L15" s="4">
         <f t="shared" si="5"/>
-        <v>3800</v>
+        <v>5700</v>
       </c>
       <c r="M15" s="4">
         <f t="shared" si="6"/>
-        <v>7600</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.2">
@@ -1711,16 +1711,16 @@
         <v>2000</v>
       </c>
       <c r="G16" s="4">
-        <f t="shared" ref="G16:I16" si="18">F16*2</f>
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" ref="G16:I16" si="18">G16*2</f>
         <v>4000</v>
       </c>
-      <c r="H16" s="4">
+      <c r="I16" s="4">
         <f t="shared" si="18"/>
         <v>8000</v>
-      </c>
-      <c r="I16" s="4">
-        <f t="shared" si="18"/>
-        <v>16000</v>
       </c>
       <c r="J16" s="4">
         <f t="shared" si="3"/>
@@ -1732,11 +1732,11 @@
       </c>
       <c r="L16" s="4">
         <f t="shared" si="5"/>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="M16" s="4">
         <f t="shared" si="6"/>
-        <v>8000</v>
+        <v>16000</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
@@ -1759,16 +1759,16 @@
         <v>2050</v>
       </c>
       <c r="G17" s="4">
-        <f t="shared" ref="G17:I17" si="19">F17*2</f>
+        <f t="shared" si="1"/>
+        <v>2050</v>
+      </c>
+      <c r="H17" s="4">
+        <f t="shared" ref="G17:I17" si="19">G17*2</f>
         <v>4100</v>
       </c>
-      <c r="H17" s="4">
+      <c r="I17" s="4">
         <f t="shared" si="19"/>
         <v>8200</v>
-      </c>
-      <c r="I17" s="4">
-        <f t="shared" si="19"/>
-        <v>16400</v>
       </c>
       <c r="J17" s="4">
         <f t="shared" si="3"/>
@@ -1780,11 +1780,11 @@
       </c>
       <c r="L17" s="4">
         <f t="shared" si="5"/>
-        <v>4100</v>
+        <v>6150</v>
       </c>
       <c r="M17" s="4">
         <f t="shared" si="6"/>
-        <v>8200</v>
+        <v>16400</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
@@ -1807,16 +1807,16 @@
         <v>2100</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" ref="G18:I18" si="20">F18*2</f>
+        <f t="shared" si="1"/>
+        <v>2100</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" ref="G18:I18" si="20">G18*2</f>
         <v>4200</v>
       </c>
-      <c r="H18" s="4">
+      <c r="I18" s="4">
         <f t="shared" si="20"/>
         <v>8400</v>
-      </c>
-      <c r="I18" s="4">
-        <f t="shared" si="20"/>
-        <v>16800</v>
       </c>
       <c r="J18" s="4">
         <f t="shared" si="3"/>
@@ -1828,11 +1828,11 @@
       </c>
       <c r="L18" s="4">
         <f t="shared" si="5"/>
-        <v>4200</v>
+        <v>6300</v>
       </c>
       <c r="M18" s="4">
         <f t="shared" si="6"/>
-        <v>8400</v>
+        <v>16800</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
@@ -1855,16 +1855,16 @@
         <v>2150</v>
       </c>
       <c r="G19" s="4">
-        <f t="shared" ref="G19:I19" si="21">F19*2</f>
+        <f t="shared" si="1"/>
+        <v>2150</v>
+      </c>
+      <c r="H19" s="4">
+        <f t="shared" ref="G19:I19" si="21">G19*2</f>
         <v>4300</v>
       </c>
-      <c r="H19" s="4">
+      <c r="I19" s="4">
         <f t="shared" si="21"/>
         <v>8600</v>
-      </c>
-      <c r="I19" s="4">
-        <f t="shared" si="21"/>
-        <v>17200</v>
       </c>
       <c r="J19" s="4">
         <f t="shared" si="3"/>
@@ -1876,11 +1876,11 @@
       </c>
       <c r="L19" s="4">
         <f t="shared" si="5"/>
-        <v>4300</v>
+        <v>6450</v>
       </c>
       <c r="M19" s="4">
         <f t="shared" si="6"/>
-        <v>8600</v>
+        <v>17200</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.2">
@@ -1903,16 +1903,16 @@
         <v>2200</v>
       </c>
       <c r="G20" s="4">
-        <f t="shared" ref="G20:I20" si="22">F20*2</f>
+        <f t="shared" si="1"/>
+        <v>2200</v>
+      </c>
+      <c r="H20" s="4">
+        <f t="shared" ref="G20:I20" si="22">G20*2</f>
         <v>4400</v>
       </c>
-      <c r="H20" s="4">
+      <c r="I20" s="4">
         <f t="shared" si="22"/>
         <v>8800</v>
-      </c>
-      <c r="I20" s="4">
-        <f t="shared" si="22"/>
-        <v>17600</v>
       </c>
       <c r="J20" s="4">
         <f t="shared" si="3"/>
@@ -1924,11 +1924,11 @@
       </c>
       <c r="L20" s="4">
         <f t="shared" si="5"/>
-        <v>4400</v>
+        <v>6600</v>
       </c>
       <c r="M20" s="4">
         <f t="shared" si="6"/>
-        <v>8800</v>
+        <v>17600</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
@@ -1951,16 +1951,16 @@
         <v>2250</v>
       </c>
       <c r="G21" s="4">
-        <f t="shared" ref="G21:I21" si="23">F21*2</f>
+        <f t="shared" si="1"/>
+        <v>2250</v>
+      </c>
+      <c r="H21" s="4">
+        <f t="shared" ref="G21:I21" si="23">G21*2</f>
         <v>4500</v>
       </c>
-      <c r="H21" s="4">
+      <c r="I21" s="4">
         <f t="shared" si="23"/>
         <v>9000</v>
-      </c>
-      <c r="I21" s="4">
-        <f t="shared" si="23"/>
-        <v>18000</v>
       </c>
       <c r="J21" s="4">
         <f t="shared" si="3"/>
@@ -1972,11 +1972,11 @@
       </c>
       <c r="L21" s="4">
         <f t="shared" si="5"/>
-        <v>4500</v>
+        <v>6750</v>
       </c>
       <c r="M21" s="4">
         <f t="shared" si="6"/>
-        <v>9000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
@@ -1999,16 +1999,16 @@
         <v>2300</v>
       </c>
       <c r="G22" s="4">
-        <f t="shared" ref="G22:I22" si="24">F22*2</f>
+        <f t="shared" si="1"/>
+        <v>2300</v>
+      </c>
+      <c r="H22" s="4">
+        <f t="shared" ref="G22:I22" si="24">G22*2</f>
         <v>4600</v>
       </c>
-      <c r="H22" s="4">
+      <c r="I22" s="4">
         <f t="shared" si="24"/>
         <v>9200</v>
-      </c>
-      <c r="I22" s="4">
-        <f t="shared" si="24"/>
-        <v>18400</v>
       </c>
       <c r="J22" s="4">
         <f t="shared" si="3"/>
@@ -2020,11 +2020,11 @@
       </c>
       <c r="L22" s="4">
         <f t="shared" si="5"/>
-        <v>4600</v>
+        <v>6900</v>
       </c>
       <c r="M22" s="4">
         <f t="shared" si="6"/>
-        <v>9200</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.2">
@@ -2047,16 +2047,16 @@
         <v>2350</v>
       </c>
       <c r="G23" s="4">
-        <f t="shared" ref="G23:I23" si="25">F23*2</f>
+        <f t="shared" si="1"/>
+        <v>2350</v>
+      </c>
+      <c r="H23" s="4">
+        <f t="shared" ref="G23:I23" si="25">G23*2</f>
         <v>4700</v>
       </c>
-      <c r="H23" s="4">
+      <c r="I23" s="4">
         <f t="shared" si="25"/>
         <v>9400</v>
-      </c>
-      <c r="I23" s="4">
-        <f t="shared" si="25"/>
-        <v>18800</v>
       </c>
       <c r="J23" s="4">
         <f t="shared" si="3"/>
@@ -2068,11 +2068,11 @@
       </c>
       <c r="L23" s="4">
         <f t="shared" si="5"/>
-        <v>4700</v>
+        <v>7050</v>
       </c>
       <c r="M23" s="4">
         <f t="shared" si="6"/>
-        <v>9400</v>
+        <v>18800</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.2">
@@ -2095,16 +2095,16 @@
         <v>2400</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" ref="G24:I24" si="26">F24*2</f>
+        <f t="shared" si="1"/>
+        <v>2400</v>
+      </c>
+      <c r="H24" s="4">
+        <f t="shared" ref="G24:I24" si="26">G24*2</f>
         <v>4800</v>
       </c>
-      <c r="H24" s="4">
+      <c r="I24" s="4">
         <f t="shared" si="26"/>
         <v>9600</v>
-      </c>
-      <c r="I24" s="4">
-        <f t="shared" si="26"/>
-        <v>19200</v>
       </c>
       <c r="J24" s="4">
         <f t="shared" si="3"/>
@@ -2116,11 +2116,11 @@
       </c>
       <c r="L24" s="4">
         <f t="shared" si="5"/>
-        <v>4800</v>
+        <v>7200</v>
       </c>
       <c r="M24" s="4">
         <f t="shared" si="6"/>
-        <v>9600</v>
+        <v>19200</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
@@ -2143,16 +2143,16 @@
         <v>2450</v>
       </c>
       <c r="G25" s="4">
-        <f t="shared" ref="G25:I25" si="27">F25*2</f>
+        <f t="shared" si="1"/>
+        <v>2450</v>
+      </c>
+      <c r="H25" s="4">
+        <f t="shared" ref="G25:I25" si="27">G25*2</f>
         <v>4900</v>
       </c>
-      <c r="H25" s="4">
+      <c r="I25" s="4">
         <f t="shared" si="27"/>
         <v>9800</v>
-      </c>
-      <c r="I25" s="4">
-        <f t="shared" si="27"/>
-        <v>19600</v>
       </c>
       <c r="J25" s="4">
         <f t="shared" si="3"/>
@@ -2164,11 +2164,11 @@
       </c>
       <c r="L25" s="4">
         <f t="shared" si="5"/>
-        <v>4900</v>
+        <v>7350</v>
       </c>
       <c r="M25" s="4">
         <f t="shared" si="6"/>
-        <v>9800</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
@@ -2191,16 +2191,16 @@
         <v>2500</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" ref="G26:I26" si="28">F26*2</f>
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="H26" s="4">
+        <f t="shared" ref="G26:I26" si="28">G26*2</f>
         <v>5000</v>
       </c>
-      <c r="H26" s="4">
+      <c r="I26" s="4">
         <f t="shared" si="28"/>
         <v>10000</v>
-      </c>
-      <c r="I26" s="4">
-        <f t="shared" si="28"/>
-        <v>20000</v>
       </c>
       <c r="J26" s="4">
         <f t="shared" si="3"/>
@@ -2212,11 +2212,11 @@
       </c>
       <c r="L26" s="4">
         <f t="shared" si="5"/>
-        <v>5000</v>
+        <v>7500</v>
       </c>
       <c r="M26" s="4">
         <f t="shared" si="6"/>
-        <v>10000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.2">
@@ -2239,16 +2239,16 @@
         <v>1450</v>
       </c>
       <c r="G27" s="4">
-        <f t="shared" ref="G27:I27" si="29">F27*2</f>
+        <f t="shared" si="1"/>
+        <v>1450</v>
+      </c>
+      <c r="H27" s="4">
+        <f t="shared" ref="G27:I27" si="29">G27*2</f>
         <v>2900</v>
       </c>
-      <c r="H27" s="4">
+      <c r="I27" s="4">
         <f t="shared" si="29"/>
         <v>5800</v>
-      </c>
-      <c r="I27" s="4">
-        <f t="shared" si="29"/>
-        <v>11600</v>
       </c>
       <c r="J27" s="4">
         <f t="shared" si="3"/>
@@ -2260,11 +2260,11 @@
       </c>
       <c r="L27" s="4">
         <f t="shared" si="5"/>
-        <v>2900</v>
+        <v>4350</v>
       </c>
       <c r="M27" s="4">
         <f t="shared" si="6"/>
-        <v>5800</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.2">
@@ -2287,16 +2287,16 @@
         <v>1550</v>
       </c>
       <c r="G28" s="4">
-        <f t="shared" ref="G28:I28" si="30">F28*2</f>
+        <f t="shared" si="1"/>
+        <v>1550</v>
+      </c>
+      <c r="H28" s="4">
+        <f t="shared" ref="G28:I28" si="30">G28*2</f>
         <v>3100</v>
       </c>
-      <c r="H28" s="4">
+      <c r="I28" s="4">
         <f t="shared" si="30"/>
         <v>6200</v>
-      </c>
-      <c r="I28" s="4">
-        <f t="shared" si="30"/>
-        <v>12400</v>
       </c>
       <c r="J28" s="4">
         <f t="shared" si="3"/>
@@ -2308,11 +2308,11 @@
       </c>
       <c r="L28" s="4">
         <f t="shared" si="5"/>
-        <v>3100</v>
+        <v>4650</v>
       </c>
       <c r="M28" s="4">
         <f t="shared" si="6"/>
-        <v>6200</v>
+        <v>12400</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
@@ -2335,16 +2335,16 @@
         <v>1650</v>
       </c>
       <c r="G29" s="4">
-        <f t="shared" ref="G29:I29" si="31">F29*2</f>
+        <f t="shared" si="1"/>
+        <v>1650</v>
+      </c>
+      <c r="H29" s="4">
+        <f t="shared" ref="G29:I29" si="31">G29*2</f>
         <v>3300</v>
       </c>
-      <c r="H29" s="4">
+      <c r="I29" s="4">
         <f t="shared" si="31"/>
         <v>6600</v>
-      </c>
-      <c r="I29" s="4">
-        <f t="shared" si="31"/>
-        <v>13200</v>
       </c>
       <c r="J29" s="4">
         <f t="shared" si="3"/>
@@ -2356,11 +2356,11 @@
       </c>
       <c r="L29" s="4">
         <f t="shared" si="5"/>
-        <v>3300</v>
+        <v>4950</v>
       </c>
       <c r="M29" s="4">
         <f t="shared" si="6"/>
-        <v>6600</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.2">
@@ -2383,16 +2383,16 @@
         <v>1750</v>
       </c>
       <c r="G30" s="4">
-        <f t="shared" ref="G30:I30" si="32">F30*2</f>
+        <f t="shared" si="1"/>
+        <v>1750</v>
+      </c>
+      <c r="H30" s="4">
+        <f t="shared" ref="G30:I30" si="32">G30*2</f>
         <v>3500</v>
       </c>
-      <c r="H30" s="4">
+      <c r="I30" s="4">
         <f t="shared" si="32"/>
         <v>7000</v>
-      </c>
-      <c r="I30" s="4">
-        <f t="shared" si="32"/>
-        <v>14000</v>
       </c>
       <c r="J30" s="4">
         <f t="shared" si="3"/>
@@ -2404,11 +2404,11 @@
       </c>
       <c r="L30" s="4">
         <f t="shared" si="5"/>
-        <v>3500</v>
+        <v>5250</v>
       </c>
       <c r="M30" s="4">
         <f t="shared" si="6"/>
-        <v>7000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.2">
@@ -2431,16 +2431,16 @@
         <v>1850</v>
       </c>
       <c r="G31" s="4">
-        <f t="shared" ref="G31:I31" si="33">F31*2</f>
+        <f t="shared" si="1"/>
+        <v>1850</v>
+      </c>
+      <c r="H31" s="4">
+        <f t="shared" ref="G31:I31" si="33">G31*2</f>
         <v>3700</v>
       </c>
-      <c r="H31" s="4">
+      <c r="I31" s="4">
         <f t="shared" si="33"/>
         <v>7400</v>
-      </c>
-      <c r="I31" s="4">
-        <f t="shared" si="33"/>
-        <v>14800</v>
       </c>
       <c r="J31" s="4">
         <f t="shared" si="3"/>
@@ -2452,11 +2452,11 @@
       </c>
       <c r="L31" s="4">
         <f t="shared" si="5"/>
-        <v>3700</v>
+        <v>5550</v>
       </c>
       <c r="M31" s="4">
         <f t="shared" si="6"/>
-        <v>7400</v>
+        <v>14800</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.2">
@@ -2479,16 +2479,16 @@
         <v>1950</v>
       </c>
       <c r="G32" s="4">
-        <f t="shared" ref="G32:I32" si="34">F32*2</f>
+        <f t="shared" si="1"/>
+        <v>1950</v>
+      </c>
+      <c r="H32" s="4">
+        <f t="shared" ref="G32:I32" si="34">G32*2</f>
         <v>3900</v>
       </c>
-      <c r="H32" s="4">
+      <c r="I32" s="4">
         <f t="shared" si="34"/>
         <v>7800</v>
-      </c>
-      <c r="I32" s="4">
-        <f t="shared" si="34"/>
-        <v>15600</v>
       </c>
       <c r="J32" s="4">
         <f t="shared" si="3"/>
@@ -2500,11 +2500,11 @@
       </c>
       <c r="L32" s="4">
         <f t="shared" si="5"/>
-        <v>3900</v>
+        <v>5850</v>
       </c>
       <c r="M32" s="4">
         <f t="shared" si="6"/>
-        <v>7800</v>
+        <v>15600</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
@@ -2527,16 +2527,16 @@
         <v>3500</v>
       </c>
       <c r="G33" s="4">
-        <f t="shared" ref="G33:I33" si="35">F33*2</f>
+        <f t="shared" si="1"/>
+        <v>3500</v>
+      </c>
+      <c r="H33" s="4">
+        <f t="shared" ref="G33:I33" si="35">G33*2</f>
         <v>7000</v>
       </c>
-      <c r="H33" s="4">
+      <c r="I33" s="4">
         <f t="shared" si="35"/>
         <v>14000</v>
-      </c>
-      <c r="I33" s="4">
-        <f t="shared" si="35"/>
-        <v>28000</v>
       </c>
       <c r="J33" s="4">
         <f t="shared" si="3"/>
@@ -2548,11 +2548,11 @@
       </c>
       <c r="L33" s="4">
         <f t="shared" si="5"/>
-        <v>7000</v>
+        <v>10500</v>
       </c>
       <c r="M33" s="4">
         <f t="shared" si="6"/>
-        <v>14000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.2">
@@ -2575,16 +2575,16 @@
         <v>4000</v>
       </c>
       <c r="G34" s="4">
-        <f t="shared" ref="G34:I34" si="36">F34*2</f>
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="H34" s="4">
+        <f t="shared" ref="G34:I34" si="36">G34*2</f>
         <v>8000</v>
       </c>
-      <c r="H34" s="4">
+      <c r="I34" s="4">
         <f t="shared" si="36"/>
         <v>16000</v>
-      </c>
-      <c r="I34" s="4">
-        <f t="shared" si="36"/>
-        <v>32000</v>
       </c>
       <c r="J34" s="4">
         <f t="shared" si="3"/>
@@ -2596,11 +2596,11 @@
       </c>
       <c r="L34" s="4">
         <f t="shared" si="5"/>
-        <v>8000</v>
+        <v>12000</v>
       </c>
       <c r="M34" s="4">
         <f t="shared" si="6"/>
-        <v>16000</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.2">
@@ -2623,16 +2623,16 @@
         <v>4500</v>
       </c>
       <c r="G35" s="4">
-        <f t="shared" ref="G35:I35" si="37">F35*2</f>
+        <f t="shared" si="1"/>
+        <v>4500</v>
+      </c>
+      <c r="H35" s="4">
+        <f t="shared" ref="G35:I35" si="37">G35*2</f>
         <v>9000</v>
       </c>
-      <c r="H35" s="4">
+      <c r="I35" s="4">
         <f t="shared" si="37"/>
         <v>18000</v>
-      </c>
-      <c r="I35" s="4">
-        <f t="shared" si="37"/>
-        <v>36000</v>
       </c>
       <c r="J35" s="4">
         <f t="shared" si="3"/>
@@ -2644,11 +2644,11 @@
       </c>
       <c r="L35" s="4">
         <f t="shared" si="5"/>
-        <v>9000</v>
+        <v>13500</v>
       </c>
       <c r="M35" s="4">
         <f t="shared" si="6"/>
-        <v>18000</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.2">
@@ -2671,16 +2671,16 @@
         <v>5000</v>
       </c>
       <c r="G36" s="4">
-        <f t="shared" ref="G36:I36" si="38">F36*2</f>
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+      <c r="H36" s="4">
+        <f t="shared" ref="G36:I36" si="38">G36*2</f>
         <v>10000</v>
       </c>
-      <c r="H36" s="4">
+      <c r="I36" s="4">
         <f t="shared" si="38"/>
         <v>20000</v>
-      </c>
-      <c r="I36" s="4">
-        <f t="shared" si="38"/>
-        <v>40000</v>
       </c>
       <c r="J36" s="4">
         <f t="shared" si="3"/>
@@ -2692,11 +2692,11 @@
       </c>
       <c r="L36" s="4">
         <f t="shared" si="5"/>
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="M36" s="4">
         <f t="shared" si="6"/>
-        <v>20000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
@@ -2992,7 +2992,7 @@
         <v>56</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="4">
@@ -3038,7 +3038,7 @@
         <v>56</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="4">
@@ -3130,7 +3130,7 @@
         <v>57</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E46" s="3"/>
       <c r="F46" s="4">
@@ -3176,7 +3176,7 @@
         <v>57</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="4">
